--- a/data/Spravochniki/Holidays.xlsx
+++ b/data/Spravochniki/Holidays.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\RAO_Project\data\Spravochniki\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\RAO_Project\data\Spravochniki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB63C8CA-0FB4-474C-B90C-42979BBAF791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF03AE5-7CAD-40F4-9698-7B9332573E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Выходные" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -62,7 +65,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -340,160 +343,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
         <v>43885</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>43899</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>43955</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>43956</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>43962</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>44249</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>44319</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>44326</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>44361</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>44505</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>44561</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>44627</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>44683</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>44684</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>44691</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>44725</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>44981</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>45054</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>45236</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>45656</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>45657</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>45411</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>45412</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>45422</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>45656</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>45657</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>45712</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>45726</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>45779</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>45821</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
+        <v>46387</v>
       </c>
     </row>
   </sheetData>
@@ -504,32 +527,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED014FEB-0D2D-4CD8-B4ED-CDADD2FBE1F2}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
         <v>44247</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>44625</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45409</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45598</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45654</v>
       </c>
